--- a/output/gpu_prices_2026-07-27.xlsx
+++ b/output/gpu_prices_2026-07-27.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Prices" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -53,7 +50,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -61,24 +58,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -445,13 +434,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,10 +458,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Massed Compute</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>QuantaCloud</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Vast.ai</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Vultr</t>
         </is>
@@ -484,143 +485,183 @@
       </c>
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
         <v>0.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce GTX 1080</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+          <t>NVIDIA A30</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 2080 Ti</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="n">
-        <v>0.12</v>
-      </c>
+          <t>NVIDIA GeForce GTX 1080</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 3060</t>
+          <t>NVIDIA GeForce RTX 2080 Ti</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="n">
-        <v>0.08</v>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 3090</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0.24</v>
-      </c>
+          <t>NVIDIA GeForce RTX 3060</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 4060 Ti</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="n">
-        <v>0.15</v>
-      </c>
+          <t>NVIDIA GeForce RTX 3090</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 4090</t>
+          <t>NVIDIA GeForce RTX 4060 Ti</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 5060 Ti</t>
+          <t>NVIDIA GeForce RTX 4090</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="n">
-        <v>0.18</v>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 5070</t>
+          <t>NVIDIA GeForce RTX 5060 Ti</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 5090</t>
+          <t>NVIDIA GeForce RTX 5070</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="n">
-        <v>0.47</v>
-      </c>
+      <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 4000 Ada Generation</t>
+          <t>NVIDIA GeForce RTX 5090</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="n">
-        <v>0.33</v>
-      </c>
+      <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>NVIDIA RTX 4000 Ada Generation</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>NVIDIA RTX A5000</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr"/>
-      <c r="C13" s="3" t="n">
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="D13" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
